--- a/FDA 1일 섭취허용량.xlsx
+++ b/FDA 1일 섭취허용량.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a624188ccc7a469/바탕 화면/CPCA 계산기/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a624188ccc7a469/바탕 화면/nitrosamines-AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3814E1E0-2717-4537-8536-095977B0A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8475A96-5AE2-4F0D-9FD6-0BD8CAEB81F1}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{3814E1E0-2717-4537-8536-095977B0A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35E4334D-C84A-45CE-BB5A-6072462D86AC}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="3960" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26690" yWindow="5180" windowWidth="14400" windowHeight="8240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="537">
-  <si>
-    <t>N-nitroso-abacavir</t>
-  </si>
   <si>
     <t>Abacavir</t>
   </si>
@@ -1652,12 +1649,16 @@
     <t>연번</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>N-nitroso-abacavir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1687,6 +1688,11 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1708,12 +1714,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1729,6 +1736,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2059,36 +2070,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.899999999999999" x14ac:dyDescent="0.6">
       <c r="A1" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
       <c r="D2" s="1">
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -2096,16 +2107,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
       <c r="D3" s="1">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -2113,16 +2124,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -2130,16 +2141,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
       <c r="D5" s="1">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -2147,16 +2158,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -2164,16 +2175,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -2181,16 +2192,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
       <c r="D8" s="1">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -2198,16 +2209,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -2215,16 +2226,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
       <c r="D10" s="1">
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -2232,16 +2243,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
       <c r="D11" s="1">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -2249,16 +2260,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -2266,16 +2277,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
       <c r="D13" s="1">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
@@ -2283,16 +2294,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
       <c r="D14" s="1">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
@@ -2300,16 +2311,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -2317,16 +2328,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
       <c r="D16" s="1">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
@@ -2334,16 +2345,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -2351,16 +2362,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
       <c r="D18" s="1">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
@@ -2368,16 +2379,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
       <c r="D19" s="1">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -2385,16 +2396,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
       <c r="D20" s="1">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
@@ -2402,16 +2413,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
         <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -2419,16 +2430,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
         <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>44</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -2436,16 +2447,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
         <v>46</v>
       </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
       <c r="D23" s="1">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -2453,16 +2464,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
       <c r="D24" s="1">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -2470,16 +2481,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
         <v>50</v>
       </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
       <c r="D25" s="1">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
@@ -2487,16 +2498,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
         <v>52</v>
       </c>
-      <c r="C26" t="s">
-        <v>53</v>
-      </c>
       <c r="D26" s="1">
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
@@ -2504,16 +2515,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
         <v>54</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
@@ -2521,16 +2532,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
         <v>56</v>
       </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
       <c r="D28" s="1">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
@@ -2538,16 +2549,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
         <v>58</v>
       </c>
-      <c r="C29" t="s">
-        <v>59</v>
-      </c>
       <c r="D29" s="1">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -2555,16 +2566,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" t="s">
         <v>60</v>
       </c>
-      <c r="C30" t="s">
-        <v>61</v>
-      </c>
       <c r="D30" s="1">
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -2572,16 +2583,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" t="s">
         <v>62</v>
       </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
@@ -2589,16 +2600,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
         <v>64</v>
-      </c>
-      <c r="C32" t="s">
-        <v>65</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
@@ -2606,16 +2617,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" t="s">
         <v>66</v>
       </c>
-      <c r="C33" t="s">
-        <v>67</v>
-      </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
@@ -2623,16 +2634,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
         <v>68</v>
       </c>
-      <c r="C34" t="s">
-        <v>69</v>
-      </c>
       <c r="D34" s="1">
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
@@ -2640,16 +2651,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
         <v>70</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
@@ -2657,16 +2668,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
         <v>72</v>
       </c>
-      <c r="C36" t="s">
-        <v>73</v>
-      </c>
       <c r="D36" s="1">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
@@ -2674,16 +2685,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
         <v>74</v>
       </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
       <c r="D37" s="1">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
@@ -2691,16 +2702,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
         <v>76</v>
       </c>
-      <c r="C38" t="s">
-        <v>77</v>
-      </c>
       <c r="D38" s="1">
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
@@ -2708,16 +2719,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s">
         <v>78</v>
       </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
       <c r="D39" s="1">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
@@ -2725,16 +2736,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
         <v>80</v>
       </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
@@ -2742,16 +2753,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
         <v>82</v>
-      </c>
-      <c r="C41" t="s">
-        <v>83</v>
       </c>
       <c r="D41" s="1">
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
@@ -2759,16 +2770,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
         <v>84</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" s="1">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
         <v>85</v>
-      </c>
-      <c r="D42" s="1">
-        <v>4</v>
-      </c>
-      <c r="E42" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
@@ -2776,16 +2787,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" t="s">
         <v>87</v>
       </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
@@ -2793,16 +2804,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
         <v>89</v>
       </c>
-      <c r="C44" t="s">
-        <v>90</v>
-      </c>
       <c r="D44" s="1">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
@@ -2810,16 +2821,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" t="s">
         <v>91</v>
       </c>
-      <c r="C45" t="s">
-        <v>92</v>
-      </c>
       <c r="D45" s="1">
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
@@ -2827,16 +2838,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s">
         <v>93</v>
       </c>
-      <c r="C46" t="s">
-        <v>94</v>
-      </c>
       <c r="D46" s="1">
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
@@ -2844,16 +2855,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" t="s">
         <v>95</v>
       </c>
-      <c r="C47" t="s">
-        <v>96</v>
-      </c>
       <c r="D47" s="1">
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
@@ -2861,16 +2872,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" t="s">
         <v>97</v>
-      </c>
-      <c r="C48" t="s">
-        <v>98</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
@@ -2878,16 +2889,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
@@ -2895,16 +2906,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
@@ -2912,16 +2923,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
@@ -2929,16 +2940,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D52" s="1">
         <v>2</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
@@ -2946,16 +2957,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D53" s="1">
         <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
@@ -2963,16 +2974,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
@@ -2980,16 +2991,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" s="1">
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
@@ -2997,16 +3008,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" s="1">
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
@@ -3014,16 +3025,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
@@ -3031,16 +3042,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" t="s">
         <v>108</v>
       </c>
-      <c r="C58" t="s">
-        <v>109</v>
-      </c>
       <c r="D58" s="1">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
@@ -3048,16 +3059,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
         <v>110</v>
-      </c>
-      <c r="C59" t="s">
-        <v>111</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
@@ -3065,16 +3076,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" t="s">
         <v>112</v>
       </c>
-      <c r="C60" t="s">
-        <v>113</v>
-      </c>
       <c r="D60" s="1">
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
@@ -3082,16 +3093,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
@@ -3099,16 +3110,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
@@ -3116,16 +3127,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
@@ -3133,16 +3144,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
@@ -3150,16 +3161,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
       </c>
       <c r="E65" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
@@ -3167,16 +3178,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C66" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
       </c>
       <c r="E66" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
@@ -3184,16 +3195,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
@@ -3201,16 +3212,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
@@ -3218,16 +3229,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>121</v>
+      </c>
+      <c r="C69" t="s">
         <v>122</v>
-      </c>
-      <c r="C69" t="s">
-        <v>123</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
@@ -3235,16 +3246,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>123</v>
+      </c>
+      <c r="C70" t="s">
         <v>124</v>
-      </c>
-      <c r="C70" t="s">
-        <v>125</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
@@ -3252,16 +3263,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" t="s">
         <v>126</v>
       </c>
-      <c r="C71" t="s">
-        <v>127</v>
-      </c>
       <c r="D71" s="1">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
@@ -3269,16 +3280,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>127</v>
+      </c>
+      <c r="C72" t="s">
         <v>128</v>
-      </c>
-      <c r="C72" t="s">
-        <v>129</v>
       </c>
       <c r="D72" s="1">
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
@@ -3286,16 +3297,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" t="s">
         <v>130</v>
       </c>
-      <c r="C73" t="s">
-        <v>131</v>
-      </c>
       <c r="D73" s="1">
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
@@ -3303,16 +3314,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" t="s">
         <v>132</v>
       </c>
-      <c r="C74" t="s">
-        <v>133</v>
-      </c>
       <c r="D74" s="1">
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
@@ -3320,16 +3331,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" t="s">
         <v>134</v>
       </c>
-      <c r="C75" t="s">
-        <v>135</v>
-      </c>
       <c r="D75" s="1">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
@@ -3337,16 +3348,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" t="s">
         <v>136</v>
       </c>
-      <c r="C76" t="s">
-        <v>137</v>
-      </c>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
@@ -3354,16 +3365,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" t="s">
         <v>138</v>
       </c>
-      <c r="C77" t="s">
-        <v>139</v>
-      </c>
       <c r="D77" s="1">
         <v>5</v>
       </c>
       <c r="E77" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
@@ -3371,16 +3382,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" t="s">
         <v>140</v>
       </c>
-      <c r="C78" t="s">
-        <v>141</v>
-      </c>
       <c r="D78" s="1">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
@@ -3388,16 +3399,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" t="s">
         <v>142</v>
-      </c>
-      <c r="C79" t="s">
-        <v>143</v>
       </c>
       <c r="D79" s="1">
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
@@ -3405,16 +3416,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" t="s">
         <v>144</v>
       </c>
-      <c r="C80" t="s">
-        <v>145</v>
-      </c>
       <c r="D80" s="1">
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
@@ -3422,16 +3433,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>145</v>
+      </c>
+      <c r="C81" t="s">
         <v>146</v>
-      </c>
-      <c r="C81" t="s">
-        <v>147</v>
       </c>
       <c r="D81" s="1">
         <v>2</v>
       </c>
       <c r="E81" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
@@ -3439,16 +3450,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>148</v>
+      </c>
+      <c r="C82" t="s">
         <v>149</v>
       </c>
-      <c r="C82" t="s">
-        <v>150</v>
-      </c>
       <c r="D82" s="1">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
@@ -3456,16 +3467,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C83" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
@@ -3473,16 +3484,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>151</v>
+      </c>
+      <c r="C84" t="s">
         <v>152</v>
-      </c>
-      <c r="C84" t="s">
-        <v>153</v>
       </c>
       <c r="D84" s="1">
         <v>3</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
@@ -3490,16 +3501,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>153</v>
+      </c>
+      <c r="C85" t="s">
         <v>154</v>
       </c>
-      <c r="C85" t="s">
-        <v>155</v>
-      </c>
       <c r="D85" s="1">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
@@ -3507,16 +3518,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>155</v>
+      </c>
+      <c r="C86" t="s">
         <v>156</v>
       </c>
-      <c r="C86" t="s">
-        <v>157</v>
-      </c>
       <c r="D86" s="1">
         <v>5</v>
       </c>
       <c r="E86" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
@@ -3524,16 +3535,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>157</v>
+      </c>
+      <c r="C87" t="s">
         <v>158</v>
       </c>
-      <c r="C87" t="s">
-        <v>159</v>
-      </c>
       <c r="D87" s="1">
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
@@ -3541,16 +3552,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>159</v>
+      </c>
+      <c r="C88" t="s">
         <v>160</v>
       </c>
-      <c r="C88" t="s">
-        <v>161</v>
-      </c>
       <c r="D88" s="1">
         <v>5</v>
       </c>
       <c r="E88" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
@@ -3558,16 +3569,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>161</v>
+      </c>
+      <c r="C89" t="s">
         <v>162</v>
       </c>
-      <c r="C89" t="s">
-        <v>163</v>
-      </c>
       <c r="D89" s="1">
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
@@ -3575,16 +3586,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>163</v>
+      </c>
+      <c r="C90" t="s">
         <v>164</v>
       </c>
-      <c r="C90" t="s">
-        <v>165</v>
-      </c>
       <c r="D90" s="1">
         <v>4</v>
       </c>
       <c r="E90" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
@@ -3592,16 +3603,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" t="s">
         <v>166</v>
-      </c>
-      <c r="C91" t="s">
-        <v>167</v>
       </c>
       <c r="D91" s="1">
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
@@ -3609,16 +3620,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" t="s">
         <v>168</v>
-      </c>
-      <c r="C92" t="s">
-        <v>169</v>
       </c>
       <c r="D92" s="1">
         <v>3</v>
       </c>
       <c r="E92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
@@ -3626,16 +3637,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" t="s">
         <v>170</v>
       </c>
-      <c r="C93" t="s">
-        <v>171</v>
-      </c>
       <c r="D93" s="1">
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
@@ -3643,16 +3654,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>171</v>
+      </c>
+      <c r="C94" t="s">
         <v>172</v>
       </c>
-      <c r="C94" t="s">
-        <v>173</v>
-      </c>
       <c r="D94" s="1">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
@@ -3660,16 +3671,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>173</v>
+      </c>
+      <c r="C95" t="s">
         <v>174</v>
-      </c>
-      <c r="C95" t="s">
-        <v>175</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
@@ -3677,16 +3688,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>175</v>
+      </c>
+      <c r="C96" t="s">
         <v>176</v>
       </c>
-      <c r="C96" t="s">
-        <v>177</v>
-      </c>
       <c r="D96" s="1">
         <v>1</v>
       </c>
       <c r="E96" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
@@ -3694,16 +3705,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>177</v>
+      </c>
+      <c r="C97" t="s">
         <v>178</v>
       </c>
-      <c r="C97" t="s">
-        <v>179</v>
-      </c>
       <c r="D97" s="1">
         <v>5</v>
       </c>
       <c r="E97" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
@@ -3711,16 +3722,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" t="s">
         <v>180</v>
       </c>
-      <c r="C98" t="s">
-        <v>181</v>
-      </c>
       <c r="D98" s="1">
         <v>4</v>
       </c>
       <c r="E98" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
@@ -3728,16 +3739,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>181</v>
+      </c>
+      <c r="C99" t="s">
         <v>182</v>
       </c>
-      <c r="C99" t="s">
-        <v>183</v>
-      </c>
       <c r="D99" s="1">
         <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
@@ -3745,16 +3756,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>183</v>
+      </c>
+      <c r="C100" t="s">
         <v>184</v>
       </c>
-      <c r="C100" t="s">
-        <v>185</v>
-      </c>
       <c r="D100" s="1">
         <v>5</v>
       </c>
       <c r="E100" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
@@ -3762,16 +3773,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>185</v>
+      </c>
+      <c r="C101" t="s">
         <v>186</v>
       </c>
-      <c r="C101" t="s">
-        <v>187</v>
-      </c>
       <c r="D101" s="1">
         <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
@@ -3779,16 +3790,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>187</v>
+      </c>
+      <c r="C102" t="s">
         <v>188</v>
       </c>
-      <c r="C102" t="s">
-        <v>189</v>
-      </c>
       <c r="D102" s="1">
         <v>5</v>
       </c>
       <c r="E102" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
@@ -3796,16 +3807,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" t="s">
         <v>190</v>
-      </c>
-      <c r="C103" t="s">
-        <v>191</v>
       </c>
       <c r="D103" s="1">
         <v>3</v>
       </c>
       <c r="E103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
@@ -3813,16 +3824,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>191</v>
+      </c>
+      <c r="C104" t="s">
         <v>192</v>
-      </c>
-      <c r="C104" t="s">
-        <v>193</v>
       </c>
       <c r="D104" s="1">
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
@@ -3830,16 +3841,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>193</v>
+      </c>
+      <c r="C105" t="s">
         <v>194</v>
       </c>
-      <c r="C105" t="s">
-        <v>195</v>
-      </c>
       <c r="D105" s="1">
         <v>5</v>
       </c>
       <c r="E105" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
@@ -3847,16 +3858,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>195</v>
+      </c>
+      <c r="C106" t="s">
         <v>196</v>
       </c>
-      <c r="C106" t="s">
-        <v>197</v>
-      </c>
       <c r="D106" s="1">
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
@@ -3864,16 +3875,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>197</v>
+      </c>
+      <c r="C107" t="s">
         <v>198</v>
-      </c>
-      <c r="C107" t="s">
-        <v>199</v>
       </c>
       <c r="D107" s="1">
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
@@ -3881,16 +3892,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>199</v>
+      </c>
+      <c r="C108" t="s">
         <v>200</v>
-      </c>
-      <c r="C108" t="s">
-        <v>201</v>
       </c>
       <c r="D108" s="1">
         <v>2</v>
       </c>
       <c r="E108" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
@@ -3898,16 +3909,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>201</v>
+      </c>
+      <c r="C109" t="s">
         <v>202</v>
-      </c>
-      <c r="C109" t="s">
-        <v>203</v>
       </c>
       <c r="D109" s="1">
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
@@ -3915,16 +3926,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>203</v>
+      </c>
+      <c r="C110" t="s">
         <v>204</v>
       </c>
-      <c r="C110" t="s">
-        <v>205</v>
-      </c>
       <c r="D110" s="1">
         <v>4</v>
       </c>
       <c r="E110" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
@@ -3932,16 +3943,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>205</v>
+      </c>
+      <c r="C111" t="s">
         <v>206</v>
       </c>
-      <c r="C111" t="s">
-        <v>207</v>
-      </c>
       <c r="D111" s="1">
         <v>4</v>
       </c>
       <c r="E111" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.45">
@@ -3949,16 +3960,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>207</v>
+      </c>
+      <c r="C112" t="s">
         <v>208</v>
       </c>
-      <c r="C112" t="s">
-        <v>209</v>
-      </c>
       <c r="D112" s="1">
         <v>5</v>
       </c>
       <c r="E112" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
@@ -3966,16 +3977,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C113" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D113" s="1">
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
@@ -3983,16 +3994,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
+        <v>210</v>
+      </c>
+      <c r="C114" t="s">
         <v>211</v>
       </c>
-      <c r="C114" t="s">
-        <v>212</v>
-      </c>
       <c r="D114" s="1">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
@@ -4000,16 +4011,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C115" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D115" s="1">
         <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
@@ -4017,16 +4028,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>213</v>
+      </c>
+      <c r="C116" t="s">
         <v>214</v>
-      </c>
-      <c r="C116" t="s">
-        <v>215</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
       </c>
       <c r="E116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
@@ -4034,16 +4045,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>215</v>
+      </c>
+      <c r="C117" t="s">
         <v>216</v>
       </c>
-      <c r="C117" t="s">
-        <v>217</v>
-      </c>
       <c r="D117" s="1">
         <v>4</v>
       </c>
       <c r="E117" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
@@ -4051,16 +4062,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>217</v>
+      </c>
+      <c r="C118" t="s">
         <v>218</v>
       </c>
-      <c r="C118" t="s">
-        <v>219</v>
-      </c>
       <c r="D118" s="1">
         <v>4</v>
       </c>
       <c r="E118" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
@@ -4068,16 +4079,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>219</v>
+      </c>
+      <c r="C119" t="s">
         <v>220</v>
       </c>
-      <c r="C119" t="s">
-        <v>221</v>
-      </c>
       <c r="D119" s="1">
         <v>4</v>
       </c>
       <c r="E119" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
@@ -4085,16 +4096,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
+        <v>221</v>
+      </c>
+      <c r="C120" t="s">
         <v>222</v>
       </c>
-      <c r="C120" t="s">
-        <v>223</v>
-      </c>
       <c r="D120" s="1">
         <v>5</v>
       </c>
       <c r="E120" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
@@ -4102,16 +4113,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>223</v>
+      </c>
+      <c r="C121" t="s">
         <v>224</v>
       </c>
-      <c r="C121" t="s">
-        <v>225</v>
-      </c>
       <c r="D121" s="1">
         <v>5</v>
       </c>
       <c r="E121" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
@@ -4119,16 +4130,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
+        <v>225</v>
+      </c>
+      <c r="C122" t="s">
         <v>226</v>
       </c>
-      <c r="C122" t="s">
-        <v>227</v>
-      </c>
       <c r="D122" s="1">
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
@@ -4136,16 +4147,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
+        <v>227</v>
+      </c>
+      <c r="C123" t="s">
         <v>228</v>
-      </c>
-      <c r="C123" t="s">
-        <v>229</v>
       </c>
       <c r="D123" s="1">
         <v>2</v>
       </c>
       <c r="E123" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
@@ -4153,16 +4164,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>229</v>
+      </c>
+      <c r="C124" t="s">
         <v>230</v>
       </c>
-      <c r="C124" t="s">
-        <v>231</v>
-      </c>
       <c r="D124" s="1">
         <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
@@ -4170,16 +4181,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>231</v>
+      </c>
+      <c r="C125" t="s">
         <v>232</v>
       </c>
-      <c r="C125" t="s">
-        <v>233</v>
-      </c>
       <c r="D125" s="1">
         <v>5</v>
       </c>
       <c r="E125" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
@@ -4187,16 +4198,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
+        <v>233</v>
+      </c>
+      <c r="C126" t="s">
         <v>234</v>
       </c>
-      <c r="C126" t="s">
-        <v>235</v>
-      </c>
       <c r="D126" s="1">
         <v>5</v>
       </c>
       <c r="E126" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
@@ -4204,16 +4215,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
+        <v>235</v>
+      </c>
+      <c r="C127" t="s">
         <v>236</v>
       </c>
-      <c r="C127" t="s">
-        <v>237</v>
-      </c>
       <c r="D127" s="1">
         <v>5</v>
       </c>
       <c r="E127" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
@@ -4221,16 +4232,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>237</v>
+      </c>
+      <c r="C128" t="s">
         <v>238</v>
       </c>
-      <c r="C128" t="s">
-        <v>239</v>
-      </c>
       <c r="D128" s="1">
         <v>4</v>
       </c>
       <c r="E128" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
@@ -4238,16 +4249,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
+        <v>239</v>
+      </c>
+      <c r="C129" t="s">
         <v>240</v>
       </c>
-      <c r="C129" t="s">
-        <v>241</v>
-      </c>
       <c r="D129" s="1">
         <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
@@ -4255,16 +4266,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
+        <v>241</v>
+      </c>
+      <c r="C130" t="s">
         <v>242</v>
       </c>
-      <c r="C130" t="s">
-        <v>243</v>
-      </c>
       <c r="D130" s="1">
         <v>4</v>
       </c>
       <c r="E130" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
@@ -4272,16 +4283,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C131" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D131" s="1">
         <v>4</v>
       </c>
       <c r="E131" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
@@ -4289,16 +4300,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>244</v>
+      </c>
+      <c r="C132" t="s">
         <v>245</v>
       </c>
-      <c r="C132" t="s">
-        <v>246</v>
-      </c>
       <c r="D132" s="1">
         <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
@@ -4306,16 +4317,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>246</v>
+      </c>
+      <c r="C133" t="s">
         <v>247</v>
       </c>
-      <c r="C133" t="s">
-        <v>248</v>
-      </c>
       <c r="D133" s="1">
         <v>5</v>
       </c>
       <c r="E133" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
@@ -4323,16 +4334,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
+        <v>248</v>
+      </c>
+      <c r="C134" t="s">
         <v>249</v>
-      </c>
-      <c r="C134" t="s">
-        <v>250</v>
       </c>
       <c r="D134" s="1">
         <v>3</v>
       </c>
       <c r="E134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
@@ -4340,16 +4351,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
+        <v>250</v>
+      </c>
+      <c r="C135" t="s">
         <v>251</v>
       </c>
-      <c r="C135" t="s">
-        <v>252</v>
-      </c>
       <c r="D135" s="1">
         <v>5</v>
       </c>
       <c r="E135" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
@@ -4357,16 +4368,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
+        <v>252</v>
+      </c>
+      <c r="C136" t="s">
         <v>253</v>
       </c>
-      <c r="C136" t="s">
-        <v>254</v>
-      </c>
       <c r="D136" s="1">
         <v>4</v>
       </c>
       <c r="E136" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
@@ -4374,16 +4385,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C137" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D137" s="1">
         <v>4</v>
       </c>
       <c r="E137" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
@@ -4391,16 +4402,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
+        <v>255</v>
+      </c>
+      <c r="C138" t="s">
         <v>256</v>
       </c>
-      <c r="C138" t="s">
-        <v>257</v>
-      </c>
       <c r="D138" s="1">
         <v>4</v>
       </c>
       <c r="E138" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
@@ -4408,16 +4419,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C139" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D139" s="1">
         <v>4</v>
       </c>
       <c r="E139" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
@@ -4425,16 +4436,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
+        <v>258</v>
+      </c>
+      <c r="C140" t="s">
         <v>259</v>
       </c>
-      <c r="C140" t="s">
-        <v>260</v>
-      </c>
       <c r="D140" s="1">
         <v>5</v>
       </c>
       <c r="E140" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.45">
@@ -4442,16 +4453,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
+        <v>260</v>
+      </c>
+      <c r="C141" t="s">
         <v>261</v>
-      </c>
-      <c r="C141" t="s">
-        <v>262</v>
       </c>
       <c r="D141" s="1">
         <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.45">
@@ -4459,16 +4470,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
+        <v>262</v>
+      </c>
+      <c r="C142" t="s">
         <v>263</v>
       </c>
-      <c r="C142" t="s">
-        <v>264</v>
-      </c>
       <c r="D142" s="1">
         <v>5</v>
       </c>
       <c r="E142" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
@@ -4476,16 +4487,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>264</v>
+      </c>
+      <c r="C143" t="s">
         <v>265</v>
       </c>
-      <c r="C143" t="s">
-        <v>266</v>
-      </c>
       <c r="D143" s="1">
         <v>5</v>
       </c>
       <c r="E143" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
@@ -4493,16 +4504,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
+        <v>266</v>
+      </c>
+      <c r="C144" t="s">
         <v>267</v>
       </c>
-      <c r="C144" t="s">
-        <v>268</v>
-      </c>
       <c r="D144" s="1">
         <v>5</v>
       </c>
       <c r="E144" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
@@ -4510,16 +4521,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
+        <v>268</v>
+      </c>
+      <c r="C145" t="s">
         <v>269</v>
       </c>
-      <c r="C145" t="s">
-        <v>270</v>
-      </c>
       <c r="D145" s="1">
         <v>4</v>
       </c>
       <c r="E145" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
@@ -4527,16 +4538,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
+        <v>270</v>
+      </c>
+      <c r="C146" t="s">
         <v>271</v>
       </c>
-      <c r="C146" t="s">
-        <v>272</v>
-      </c>
       <c r="D146" s="1">
         <v>4</v>
       </c>
       <c r="E146" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
@@ -4544,16 +4555,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
+        <v>272</v>
+      </c>
+      <c r="C147" t="s">
         <v>273</v>
-      </c>
-      <c r="C147" t="s">
-        <v>274</v>
       </c>
       <c r="D147" s="1">
         <v>3</v>
       </c>
       <c r="E147" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
@@ -4561,16 +4572,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
+        <v>274</v>
+      </c>
+      <c r="C148" t="s">
         <v>275</v>
-      </c>
-      <c r="C148" t="s">
-        <v>276</v>
       </c>
       <c r="D148" s="1">
         <v>3</v>
       </c>
       <c r="E148" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.45">
@@ -4578,16 +4589,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
+        <v>276</v>
+      </c>
+      <c r="C149" t="s">
         <v>277</v>
-      </c>
-      <c r="C149" t="s">
-        <v>278</v>
       </c>
       <c r="D149" s="1">
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.45">
@@ -4595,16 +4606,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
+        <v>278</v>
+      </c>
+      <c r="C150" t="s">
         <v>279</v>
       </c>
-      <c r="C150" t="s">
-        <v>280</v>
-      </c>
       <c r="D150" s="1">
         <v>5</v>
       </c>
       <c r="E150" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.45">
@@ -4612,16 +4623,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
+        <v>280</v>
+      </c>
+      <c r="C151" t="s">
         <v>281</v>
       </c>
-      <c r="C151" t="s">
-        <v>282</v>
-      </c>
       <c r="D151" s="1">
         <v>4</v>
       </c>
       <c r="E151" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.45">
@@ -4629,16 +4640,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
+        <v>282</v>
+      </c>
+      <c r="C152" t="s">
         <v>283</v>
-      </c>
-      <c r="C152" t="s">
-        <v>284</v>
       </c>
       <c r="D152" s="1">
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.45">
@@ -4646,16 +4657,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
+        <v>284</v>
+      </c>
+      <c r="C153" t="s">
         <v>285</v>
       </c>
-      <c r="C153" t="s">
-        <v>286</v>
-      </c>
       <c r="D153" s="1">
         <v>4</v>
       </c>
       <c r="E153" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
@@ -4663,16 +4674,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>286</v>
+      </c>
+      <c r="C154" t="s">
         <v>287</v>
-      </c>
-      <c r="C154" t="s">
-        <v>288</v>
       </c>
       <c r="D154" s="1">
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.45">
@@ -4680,16 +4691,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C155" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D155" s="1">
         <v>3</v>
       </c>
       <c r="E155" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.45">
@@ -4697,16 +4708,16 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>289</v>
+      </c>
+      <c r="C156" t="s">
         <v>290</v>
-      </c>
-      <c r="C156" t="s">
-        <v>291</v>
       </c>
       <c r="D156" s="1">
         <v>3</v>
       </c>
       <c r="E156" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
@@ -4714,16 +4725,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>291</v>
+      </c>
+      <c r="C157" t="s">
         <v>292</v>
-      </c>
-      <c r="C157" t="s">
-        <v>293</v>
       </c>
       <c r="D157" s="1">
         <v>3</v>
       </c>
       <c r="E157" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.45">
@@ -4731,16 +4742,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>293</v>
+      </c>
+      <c r="C158" t="s">
         <v>294</v>
       </c>
-      <c r="C158" t="s">
-        <v>295</v>
-      </c>
       <c r="D158" s="1">
         <v>4</v>
       </c>
       <c r="E158" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.45">
@@ -4748,16 +4759,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C159" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D159" s="1">
         <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.45">
@@ -4765,16 +4776,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>296</v>
+      </c>
+      <c r="C160" t="s">
         <v>297</v>
       </c>
-      <c r="C160" t="s">
-        <v>298</v>
-      </c>
       <c r="D160" s="1">
         <v>5</v>
       </c>
       <c r="E160" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.45">
@@ -4782,16 +4793,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
+        <v>298</v>
+      </c>
+      <c r="C161" t="s">
         <v>299</v>
       </c>
-      <c r="C161" t="s">
-        <v>300</v>
-      </c>
       <c r="D161" s="1">
         <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.45">
@@ -4799,16 +4810,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
+        <v>300</v>
+      </c>
+      <c r="C162" t="s">
         <v>301</v>
-      </c>
-      <c r="C162" t="s">
-        <v>302</v>
       </c>
       <c r="D162" s="1">
         <v>2</v>
       </c>
       <c r="E162" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.45">
@@ -4816,16 +4827,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C163" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D163" s="1">
         <v>4</v>
       </c>
       <c r="E163" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.45">
@@ -4833,16 +4844,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C164" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D164" s="1">
         <v>3</v>
       </c>
       <c r="E164" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.45">
@@ -4850,16 +4861,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C165" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D165" s="1">
         <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.45">
@@ -4867,16 +4878,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>305</v>
+      </c>
+      <c r="C166" t="s">
         <v>306</v>
       </c>
-      <c r="C166" t="s">
-        <v>307</v>
-      </c>
       <c r="D166" s="1">
         <v>5</v>
       </c>
       <c r="E166" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.45">
@@ -4884,16 +4895,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>307</v>
+      </c>
+      <c r="C167" t="s">
         <v>308</v>
       </c>
-      <c r="C167" t="s">
-        <v>309</v>
-      </c>
       <c r="D167" s="1">
         <v>4</v>
       </c>
       <c r="E167" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.45">
@@ -4901,16 +4912,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
+        <v>309</v>
+      </c>
+      <c r="C168" t="s">
         <v>310</v>
-      </c>
-      <c r="C168" t="s">
-        <v>311</v>
       </c>
       <c r="D168" s="1">
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.45">
@@ -4918,16 +4929,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C169" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D169" s="1">
         <v>5</v>
       </c>
       <c r="E169" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.45">
@@ -4935,16 +4946,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
+        <v>312</v>
+      </c>
+      <c r="C170" t="s">
         <v>313</v>
       </c>
-      <c r="C170" t="s">
-        <v>314</v>
-      </c>
       <c r="D170" s="1">
         <v>5</v>
       </c>
       <c r="E170" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.45">
@@ -4952,16 +4963,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
+        <v>314</v>
+      </c>
+      <c r="C171" t="s">
         <v>315</v>
       </c>
-      <c r="C171" t="s">
-        <v>316</v>
-      </c>
       <c r="D171" s="1">
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.45">
@@ -4969,16 +4980,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
+        <v>316</v>
+      </c>
+      <c r="C172" t="s">
         <v>317</v>
       </c>
-      <c r="C172" t="s">
-        <v>318</v>
-      </c>
       <c r="D172" s="1">
         <v>5</v>
       </c>
       <c r="E172" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.45">
@@ -4986,16 +4997,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>318</v>
+      </c>
+      <c r="C173" t="s">
         <v>319</v>
       </c>
-      <c r="C173" t="s">
-        <v>320</v>
-      </c>
       <c r="D173" s="1">
         <v>5</v>
       </c>
       <c r="E173" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.45">
@@ -5003,16 +5014,16 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>320</v>
+      </c>
+      <c r="C174" t="s">
         <v>321</v>
       </c>
-      <c r="C174" t="s">
-        <v>322</v>
-      </c>
       <c r="D174" s="1">
         <v>5</v>
       </c>
       <c r="E174" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.45">
@@ -5020,16 +5031,16 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>322</v>
+      </c>
+      <c r="C175" t="s">
         <v>323</v>
       </c>
-      <c r="C175" t="s">
-        <v>324</v>
-      </c>
       <c r="D175" s="1">
         <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.45">
@@ -5037,16 +5048,16 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C176" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D176" s="1">
         <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.45">
@@ -5054,16 +5065,16 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C177" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D177" s="1">
         <v>3</v>
       </c>
       <c r="E177" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.45">
@@ -5071,16 +5082,16 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>326</v>
+      </c>
+      <c r="C178" t="s">
         <v>327</v>
       </c>
-      <c r="C178" t="s">
-        <v>328</v>
-      </c>
       <c r="D178" s="1">
         <v>1</v>
       </c>
       <c r="E178" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.45">
@@ -5088,16 +5099,16 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>328</v>
+      </c>
+      <c r="C179" t="s">
         <v>329</v>
       </c>
-      <c r="C179" t="s">
-        <v>330</v>
-      </c>
       <c r="D179" s="1">
         <v>5</v>
       </c>
       <c r="E179" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.45">
@@ -5105,16 +5116,16 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
+        <v>330</v>
+      </c>
+      <c r="C180" t="s">
         <v>331</v>
       </c>
-      <c r="C180" t="s">
-        <v>332</v>
-      </c>
       <c r="D180" s="1">
         <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.45">
@@ -5122,16 +5133,16 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>332</v>
+      </c>
+      <c r="C181" t="s">
         <v>333</v>
       </c>
-      <c r="C181" t="s">
-        <v>334</v>
-      </c>
       <c r="D181" s="1">
         <v>5</v>
       </c>
       <c r="E181" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.45">
@@ -5139,16 +5150,16 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>334</v>
+      </c>
+      <c r="C182" t="s">
         <v>335</v>
       </c>
-      <c r="C182" t="s">
-        <v>336</v>
-      </c>
       <c r="D182" s="1">
         <v>4</v>
       </c>
       <c r="E182" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.45">
@@ -5156,16 +5167,16 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
+        <v>336</v>
+      </c>
+      <c r="C183" t="s">
         <v>337</v>
-      </c>
-      <c r="C183" t="s">
-        <v>338</v>
       </c>
       <c r="D183" s="1">
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
@@ -5173,16 +5184,16 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C184" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D184" s="1">
         <v>3</v>
       </c>
       <c r="E184" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
@@ -5190,16 +5201,16 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C185" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D185" s="1">
         <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.45">
@@ -5207,16 +5218,16 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>340</v>
+      </c>
+      <c r="C186" t="s">
         <v>341</v>
       </c>
-      <c r="C186" t="s">
-        <v>342</v>
-      </c>
       <c r="D186" s="1">
         <v>4</v>
       </c>
       <c r="E186" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.45">
@@ -5224,16 +5235,16 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>342</v>
+      </c>
+      <c r="C187" t="s">
         <v>343</v>
       </c>
-      <c r="C187" t="s">
-        <v>344</v>
-      </c>
       <c r="D187" s="1">
         <v>4</v>
       </c>
       <c r="E187" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.45">
@@ -5241,16 +5252,16 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C188" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D188" s="1">
         <v>5</v>
       </c>
       <c r="E188" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
@@ -5258,16 +5269,16 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>345</v>
+      </c>
+      <c r="C189" t="s">
         <v>346</v>
       </c>
-      <c r="C189" t="s">
-        <v>347</v>
-      </c>
       <c r="D189" s="1">
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.45">
@@ -5275,16 +5286,16 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
+        <v>347</v>
+      </c>
+      <c r="C190" t="s">
         <v>348</v>
-      </c>
-      <c r="C190" t="s">
-        <v>349</v>
       </c>
       <c r="D190" s="1">
         <v>3</v>
       </c>
       <c r="E190" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
@@ -5292,16 +5303,16 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>349</v>
+      </c>
+      <c r="C191" t="s">
         <v>350</v>
       </c>
-      <c r="C191" t="s">
-        <v>351</v>
-      </c>
       <c r="D191" s="1">
         <v>4</v>
       </c>
       <c r="E191" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.45">
@@ -5309,16 +5320,16 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>351</v>
+      </c>
+      <c r="C192" t="s">
         <v>352</v>
-      </c>
-      <c r="C192" t="s">
-        <v>353</v>
       </c>
       <c r="D192" s="1">
         <v>2</v>
       </c>
       <c r="E192" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
@@ -5326,16 +5337,16 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>353</v>
+      </c>
+      <c r="C193" t="s">
         <v>354</v>
       </c>
-      <c r="C193" t="s">
-        <v>355</v>
-      </c>
       <c r="D193" s="1">
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
@@ -5343,16 +5354,16 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>355</v>
+      </c>
+      <c r="C194" t="s">
         <v>356</v>
       </c>
-      <c r="C194" t="s">
-        <v>357</v>
-      </c>
       <c r="D194" s="1">
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
@@ -5360,16 +5371,16 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>357</v>
+      </c>
+      <c r="C195" t="s">
         <v>358</v>
       </c>
-      <c r="C195" t="s">
-        <v>359</v>
-      </c>
       <c r="D195" s="1">
         <v>5</v>
       </c>
       <c r="E195" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.45">
@@ -5377,16 +5388,16 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
+        <v>359</v>
+      </c>
+      <c r="C196" t="s">
         <v>360</v>
       </c>
-      <c r="C196" t="s">
-        <v>361</v>
-      </c>
       <c r="D196" s="1">
         <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
@@ -5394,16 +5405,16 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>361</v>
+      </c>
+      <c r="C197" t="s">
         <v>362</v>
-      </c>
-      <c r="C197" t="s">
-        <v>363</v>
       </c>
       <c r="D197" s="1">
         <v>2</v>
       </c>
       <c r="E197" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.45">
@@ -5411,16 +5422,16 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
+        <v>363</v>
+      </c>
+      <c r="C198" t="s">
         <v>364</v>
       </c>
-      <c r="C198" t="s">
-        <v>365</v>
-      </c>
       <c r="D198" s="1">
         <v>1</v>
       </c>
       <c r="E198" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
@@ -5428,16 +5439,16 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
+        <v>365</v>
+      </c>
+      <c r="C199" t="s">
         <v>366</v>
       </c>
-      <c r="C199" t="s">
-        <v>367</v>
-      </c>
       <c r="D199" s="1">
         <v>4</v>
       </c>
       <c r="E199" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.45">
@@ -5445,16 +5456,16 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
+        <v>367</v>
+      </c>
+      <c r="C200" t="s">
         <v>368</v>
       </c>
-      <c r="C200" t="s">
-        <v>369</v>
-      </c>
       <c r="D200" s="1">
         <v>4</v>
       </c>
       <c r="E200" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
@@ -5462,16 +5473,16 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C201" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D201" s="1">
         <v>2</v>
       </c>
       <c r="E201" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.45">
@@ -5479,16 +5490,16 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
+        <v>370</v>
+      </c>
+      <c r="C202" t="s">
         <v>371</v>
-      </c>
-      <c r="C202" t="s">
-        <v>372</v>
       </c>
       <c r="D202" s="1">
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
@@ -5496,16 +5507,16 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C203" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D203" s="1">
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.45">
@@ -5513,16 +5524,16 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C204" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D204" s="1">
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
@@ -5530,16 +5541,16 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
+        <v>374</v>
+      </c>
+      <c r="C205" t="s">
         <v>375</v>
       </c>
-      <c r="C205" t="s">
-        <v>376</v>
-      </c>
       <c r="D205" s="1">
         <v>5</v>
       </c>
       <c r="E205" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.45">
@@ -5547,16 +5558,16 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
+        <v>376</v>
+      </c>
+      <c r="C206" t="s">
         <v>377</v>
-      </c>
-      <c r="C206" t="s">
-        <v>378</v>
       </c>
       <c r="D206" s="1">
         <v>3</v>
       </c>
       <c r="E206" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
@@ -5564,16 +5575,16 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
+        <v>378</v>
+      </c>
+      <c r="C207" t="s">
         <v>379</v>
       </c>
-      <c r="C207" t="s">
-        <v>380</v>
-      </c>
       <c r="D207" s="1">
         <v>4</v>
       </c>
       <c r="E207" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
@@ -5581,16 +5592,16 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
+        <v>380</v>
+      </c>
+      <c r="C208" t="s">
         <v>381</v>
       </c>
-      <c r="C208" t="s">
-        <v>382</v>
-      </c>
       <c r="D208" s="1">
         <v>5</v>
       </c>
       <c r="E208" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.45">
@@ -5598,16 +5609,16 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
+        <v>382</v>
+      </c>
+      <c r="C209" t="s">
         <v>383</v>
       </c>
-      <c r="C209" t="s">
-        <v>384</v>
-      </c>
       <c r="D209" s="1">
         <v>4</v>
       </c>
       <c r="E209" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
@@ -5615,16 +5626,16 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
+        <v>384</v>
+      </c>
+      <c r="C210" t="s">
         <v>385</v>
-      </c>
-      <c r="C210" t="s">
-        <v>386</v>
       </c>
       <c r="D210" s="1">
         <v>3</v>
       </c>
       <c r="E210" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.45">
@@ -5632,16 +5643,16 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
+        <v>386</v>
+      </c>
+      <c r="C211" t="s">
         <v>387</v>
-      </c>
-      <c r="C211" t="s">
-        <v>388</v>
       </c>
       <c r="D211" s="1">
         <v>2</v>
       </c>
       <c r="E211" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
@@ -5649,16 +5660,16 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
+        <v>388</v>
+      </c>
+      <c r="C212" t="s">
         <v>389</v>
       </c>
-      <c r="C212" t="s">
-        <v>390</v>
-      </c>
       <c r="D212" s="1">
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.45">
@@ -5666,16 +5677,16 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
+        <v>390</v>
+      </c>
+      <c r="C213" t="s">
         <v>391</v>
       </c>
-      <c r="C213" t="s">
-        <v>392</v>
-      </c>
       <c r="D213" s="1">
         <v>4</v>
       </c>
       <c r="E213" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
@@ -5683,16 +5694,16 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
+        <v>392</v>
+      </c>
+      <c r="C214" t="s">
         <v>393</v>
-      </c>
-      <c r="C214" t="s">
-        <v>394</v>
       </c>
       <c r="D214" s="1">
         <v>3</v>
       </c>
       <c r="E214" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.45">
@@ -5700,16 +5711,16 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
+        <v>394</v>
+      </c>
+      <c r="C215" t="s">
         <v>395</v>
       </c>
-      <c r="C215" t="s">
+      <c r="D215" s="1">
+        <v>1</v>
+      </c>
+      <c r="E215" t="s">
         <v>396</v>
-      </c>
-      <c r="D215" s="1">
-        <v>1</v>
-      </c>
-      <c r="E215" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
@@ -5717,16 +5728,16 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
+        <v>397</v>
+      </c>
+      <c r="C216" t="s">
         <v>398</v>
       </c>
-      <c r="C216" t="s">
-        <v>399</v>
-      </c>
       <c r="D216" s="1">
         <v>4</v>
       </c>
       <c r="E216" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.45">
@@ -5734,16 +5745,16 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
+        <v>399</v>
+      </c>
+      <c r="C217" t="s">
         <v>400</v>
       </c>
-      <c r="C217" t="s">
-        <v>401</v>
-      </c>
       <c r="D217" s="1">
         <v>1</v>
       </c>
       <c r="E217" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.45">
@@ -5751,16 +5762,16 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
+        <v>401</v>
+      </c>
+      <c r="C218" t="s">
         <v>402</v>
-      </c>
-      <c r="C218" t="s">
-        <v>403</v>
       </c>
       <c r="D218" s="1">
         <v>3</v>
       </c>
       <c r="E218" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.45">
@@ -5768,16 +5779,16 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
+        <v>403</v>
+      </c>
+      <c r="C219" t="s">
         <v>404</v>
       </c>
-      <c r="C219" t="s">
-        <v>405</v>
-      </c>
       <c r="D219" s="1">
         <v>5</v>
       </c>
       <c r="E219" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.45">
@@ -5785,16 +5796,16 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
+        <v>405</v>
+      </c>
+      <c r="C220" t="s">
         <v>406</v>
-      </c>
-      <c r="C220" t="s">
-        <v>407</v>
       </c>
       <c r="D220" s="1">
         <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.45">
@@ -5802,16 +5813,16 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
+        <v>407</v>
+      </c>
+      <c r="C221" t="s">
         <v>408</v>
-      </c>
-      <c r="C221" t="s">
-        <v>409</v>
       </c>
       <c r="D221" s="1">
         <v>2</v>
       </c>
       <c r="E221" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.45">
@@ -5819,16 +5830,16 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
+        <v>409</v>
+      </c>
+      <c r="C222" t="s">
         <v>410</v>
       </c>
-      <c r="C222" t="s">
-        <v>411</v>
-      </c>
       <c r="D222" s="1">
         <v>5</v>
       </c>
       <c r="E222" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.45">
@@ -5836,16 +5847,16 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
+        <v>411</v>
+      </c>
+      <c r="C223" t="s">
         <v>412</v>
       </c>
-      <c r="C223" t="s">
-        <v>413</v>
-      </c>
       <c r="D223" s="1">
         <v>1</v>
       </c>
       <c r="E223" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.45">
@@ -5853,16 +5864,16 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C224" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D224" s="1">
         <v>3</v>
       </c>
       <c r="E224" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.45">
@@ -5870,16 +5881,16 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C225" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D225" s="1">
         <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.45">
@@ -5887,16 +5898,16 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
+        <v>415</v>
+      </c>
+      <c r="C226" t="s">
         <v>416</v>
-      </c>
-      <c r="C226" t="s">
-        <v>417</v>
       </c>
       <c r="D226" s="1">
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.45">
@@ -5904,16 +5915,16 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
+        <v>417</v>
+      </c>
+      <c r="C227" t="s">
         <v>418</v>
-      </c>
-      <c r="C227" t="s">
-        <v>419</v>
       </c>
       <c r="D227" s="1">
         <v>3</v>
       </c>
       <c r="E227" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.45">
@@ -5921,16 +5932,16 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
+        <v>419</v>
+      </c>
+      <c r="C228" t="s">
         <v>420</v>
       </c>
-      <c r="C228" t="s">
-        <v>421</v>
-      </c>
       <c r="D228" s="1">
         <v>5</v>
       </c>
       <c r="E228" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.45">
@@ -5938,16 +5949,16 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C229" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D229" s="1">
         <v>3</v>
       </c>
       <c r="E229" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.45">
@@ -5955,16 +5966,16 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
+        <v>422</v>
+      </c>
+      <c r="C230" t="s">
         <v>423</v>
       </c>
-      <c r="C230" t="s">
-        <v>424</v>
-      </c>
       <c r="D230" s="1">
         <v>5</v>
       </c>
       <c r="E230" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.45">
@@ -5972,16 +5983,16 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
+        <v>424</v>
+      </c>
+      <c r="C231" t="s">
         <v>425</v>
-      </c>
-      <c r="C231" t="s">
-        <v>426</v>
       </c>
       <c r="D231" s="1">
         <v>3</v>
       </c>
       <c r="E231" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.45">
@@ -5989,16 +6000,16 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
+        <v>427</v>
+      </c>
+      <c r="C232" t="s">
         <v>428</v>
-      </c>
-      <c r="C232" t="s">
-        <v>429</v>
       </c>
       <c r="D232" s="1">
         <v>3</v>
       </c>
       <c r="E232" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.45">
@@ -6006,16 +6017,16 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
+        <v>429</v>
+      </c>
+      <c r="C233" t="s">
         <v>430</v>
       </c>
-      <c r="C233" t="s">
-        <v>431</v>
-      </c>
       <c r="D233" s="1">
         <v>5</v>
       </c>
       <c r="E233" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.45">
@@ -6023,16 +6034,16 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C234" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D234" s="1">
         <v>5</v>
       </c>
       <c r="E234" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.45">
@@ -6040,16 +6051,16 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
+        <v>432</v>
+      </c>
+      <c r="C235" t="s">
         <v>433</v>
       </c>
-      <c r="C235" t="s">
-        <v>434</v>
-      </c>
       <c r="D235" s="1">
         <v>5</v>
       </c>
       <c r="E235" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.45">
@@ -6057,16 +6068,16 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
+        <v>434</v>
+      </c>
+      <c r="C236" t="s">
         <v>435</v>
       </c>
-      <c r="C236" t="s">
-        <v>436</v>
-      </c>
       <c r="D236" s="1">
         <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.45">
@@ -6074,16 +6085,16 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
+        <v>436</v>
+      </c>
+      <c r="C237" t="s">
         <v>437</v>
-      </c>
-      <c r="C237" t="s">
-        <v>438</v>
       </c>
       <c r="D237" s="1">
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.45">
@@ -6091,16 +6102,16 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
+        <v>438</v>
+      </c>
+      <c r="C238" t="s">
         <v>439</v>
       </c>
-      <c r="C238" t="s">
-        <v>440</v>
-      </c>
       <c r="D238" s="1">
         <v>1</v>
       </c>
       <c r="E238" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.45">
@@ -6108,16 +6119,16 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
+        <v>440</v>
+      </c>
+      <c r="C239" t="s">
         <v>441</v>
       </c>
-      <c r="C239" t="s">
-        <v>442</v>
-      </c>
       <c r="D239" s="1">
         <v>5</v>
       </c>
       <c r="E239" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.45">
@@ -6125,16 +6136,16 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
+        <v>442</v>
+      </c>
+      <c r="C240" t="s">
         <v>443</v>
-      </c>
-      <c r="C240" t="s">
-        <v>444</v>
       </c>
       <c r="D240" s="1">
         <v>3</v>
       </c>
       <c r="E240" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.45">
@@ -6142,16 +6153,16 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
+        <v>444</v>
+      </c>
+      <c r="C241" t="s">
         <v>445</v>
-      </c>
-      <c r="C241" t="s">
-        <v>446</v>
       </c>
       <c r="D241" s="1">
         <v>3</v>
       </c>
       <c r="E241" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.45">
@@ -6159,16 +6170,16 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
+        <v>446</v>
+      </c>
+      <c r="C242" t="s">
         <v>447</v>
       </c>
-      <c r="C242" t="s">
-        <v>448</v>
-      </c>
       <c r="D242" s="1">
         <v>4</v>
       </c>
       <c r="E242" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.45">
@@ -6176,16 +6187,16 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C243" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D243" s="1">
         <v>5</v>
       </c>
       <c r="E243" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.45">
@@ -6193,16 +6204,16 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
+        <v>449</v>
+      </c>
+      <c r="C244" t="s">
         <v>450</v>
-      </c>
-      <c r="C244" t="s">
-        <v>451</v>
       </c>
       <c r="D244" s="1">
         <v>3</v>
       </c>
       <c r="E244" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.45">
@@ -6210,16 +6221,16 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
+        <v>451</v>
+      </c>
+      <c r="C245" t="s">
         <v>452</v>
-      </c>
-      <c r="C245" t="s">
-        <v>453</v>
       </c>
       <c r="D245" s="1">
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.45">
@@ -6227,16 +6238,16 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
+        <v>454</v>
+      </c>
+      <c r="C246" t="s">
         <v>455</v>
       </c>
-      <c r="C246" t="s">
-        <v>456</v>
-      </c>
       <c r="D246" s="1">
         <v>4</v>
       </c>
       <c r="E246" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.45">
@@ -6244,16 +6255,16 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
+        <v>456</v>
+      </c>
+      <c r="C247" t="s">
         <v>457</v>
-      </c>
-      <c r="C247" t="s">
-        <v>458</v>
       </c>
       <c r="D247" s="1">
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.45">
@@ -6261,16 +6272,16 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
+        <v>458</v>
+      </c>
+      <c r="C248" t="s">
         <v>459</v>
       </c>
-      <c r="C248" t="s">
-        <v>460</v>
-      </c>
       <c r="D248" s="1">
         <v>4</v>
       </c>
       <c r="E248" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.45">
@@ -6278,16 +6289,16 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
+        <v>460</v>
+      </c>
+      <c r="C249" t="s">
         <v>461</v>
-      </c>
-      <c r="C249" t="s">
-        <v>462</v>
       </c>
       <c r="D249" s="1">
         <v>2</v>
       </c>
       <c r="E249" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.45">
@@ -6295,16 +6306,16 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C250" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D250" s="1">
         <v>2</v>
       </c>
       <c r="E250" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.45">
@@ -6312,16 +6323,16 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
+        <v>463</v>
+      </c>
+      <c r="C251" t="s">
         <v>464</v>
       </c>
-      <c r="C251" t="s">
-        <v>465</v>
-      </c>
       <c r="D251" s="1">
         <v>4</v>
       </c>
       <c r="E251" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.45">
@@ -6329,16 +6340,16 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
+        <v>465</v>
+      </c>
+      <c r="C252" t="s">
         <v>466</v>
       </c>
-      <c r="C252" t="s">
-        <v>467</v>
-      </c>
       <c r="D252" s="1">
         <v>1</v>
       </c>
       <c r="E252" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.45">
@@ -6346,16 +6357,16 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
+        <v>467</v>
+      </c>
+      <c r="C253" t="s">
         <v>468</v>
       </c>
-      <c r="C253" t="s">
-        <v>469</v>
-      </c>
       <c r="D253" s="1">
         <v>5</v>
       </c>
       <c r="E253" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.45">
@@ -6363,16 +6374,16 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
+        <v>469</v>
+      </c>
+      <c r="C254" t="s">
         <v>470</v>
       </c>
-      <c r="C254" t="s">
-        <v>471</v>
-      </c>
       <c r="D254" s="1">
         <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.45">
@@ -6380,16 +6391,16 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
+        <v>471</v>
+      </c>
+      <c r="C255" t="s">
         <v>472</v>
       </c>
-      <c r="C255" t="s">
-        <v>473</v>
-      </c>
       <c r="D255" s="1">
         <v>4</v>
       </c>
       <c r="E255" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.45">
@@ -6397,16 +6408,16 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
+        <v>473</v>
+      </c>
+      <c r="C256" t="s">
         <v>474</v>
       </c>
-      <c r="C256" t="s">
-        <v>475</v>
-      </c>
       <c r="D256" s="1">
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.45">
@@ -6414,16 +6425,16 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
+        <v>475</v>
+      </c>
+      <c r="C257" t="s">
         <v>476</v>
-      </c>
-      <c r="C257" t="s">
-        <v>477</v>
       </c>
       <c r="D257" s="1">
         <v>3</v>
       </c>
       <c r="E257" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.45">
@@ -6431,16 +6442,16 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C258" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D258" s="1">
         <v>4</v>
       </c>
       <c r="E258" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.45">
@@ -6448,16 +6459,16 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C259" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D259" s="1">
         <v>4</v>
       </c>
       <c r="E259" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.45">
@@ -6465,16 +6476,16 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C260" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D260" s="1">
         <v>5</v>
       </c>
       <c r="E260" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.45">
@@ -6482,16 +6493,16 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
+        <v>480</v>
+      </c>
+      <c r="C261" t="s">
         <v>481</v>
       </c>
-      <c r="C261" t="s">
-        <v>482</v>
-      </c>
       <c r="D261" s="1">
         <v>4</v>
       </c>
       <c r="E261" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.45">
@@ -6499,16 +6510,16 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
+        <v>482</v>
+      </c>
+      <c r="C262" t="s">
         <v>483</v>
       </c>
-      <c r="C262" t="s">
-        <v>484</v>
-      </c>
       <c r="D262" s="1">
         <v>5</v>
       </c>
       <c r="E262" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.45">
@@ -6516,16 +6527,16 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
+        <v>484</v>
+      </c>
+      <c r="C263" t="s">
         <v>485</v>
       </c>
-      <c r="C263" t="s">
-        <v>486</v>
-      </c>
       <c r="D263" s="1">
         <v>1</v>
       </c>
       <c r="E263" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.45">
@@ -6533,16 +6544,16 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C264" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D264" s="1">
         <v>3</v>
       </c>
       <c r="E264" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.45">
@@ -6550,16 +6561,16 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
+        <v>487</v>
+      </c>
+      <c r="C265" t="s">
         <v>488</v>
-      </c>
-      <c r="C265" t="s">
-        <v>489</v>
       </c>
       <c r="D265" s="1">
         <v>3</v>
       </c>
       <c r="E265" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.45">
@@ -6567,16 +6578,16 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
+        <v>489</v>
+      </c>
+      <c r="C266" t="s">
         <v>490</v>
       </c>
-      <c r="C266" t="s">
-        <v>491</v>
-      </c>
       <c r="D266" s="1">
         <v>1</v>
       </c>
       <c r="E266" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.45">
@@ -6584,16 +6595,16 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
+        <v>491</v>
+      </c>
+      <c r="C267" t="s">
         <v>492</v>
       </c>
-      <c r="C267" t="s">
-        <v>493</v>
-      </c>
       <c r="D267" s="1">
         <v>5</v>
       </c>
       <c r="E267" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.45">
@@ -6601,16 +6612,16 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
+        <v>493</v>
+      </c>
+      <c r="C268" t="s">
         <v>494</v>
-      </c>
-      <c r="C268" t="s">
-        <v>495</v>
       </c>
       <c r="D268" s="1">
         <v>3</v>
       </c>
       <c r="E268" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.45">
@@ -6618,16 +6629,16 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C269" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D269" s="1">
         <v>2</v>
       </c>
       <c r="E269" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.45">
@@ -6635,16 +6646,16 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C270" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D270" s="1">
         <v>5</v>
       </c>
       <c r="E270" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.45">
@@ -6652,16 +6663,16 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
+        <v>497</v>
+      </c>
+      <c r="C271" t="s">
         <v>498</v>
       </c>
-      <c r="C271" t="s">
-        <v>499</v>
-      </c>
       <c r="D271" s="1">
         <v>5</v>
       </c>
       <c r="E271" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.45">
@@ -6669,16 +6680,16 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
+        <v>499</v>
+      </c>
+      <c r="C272" t="s">
         <v>500</v>
       </c>
-      <c r="C272" t="s">
-        <v>501</v>
-      </c>
       <c r="D272" s="1">
         <v>4</v>
       </c>
       <c r="E272" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.45">
@@ -6686,16 +6697,16 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
+        <v>501</v>
+      </c>
+      <c r="C273" t="s">
         <v>502</v>
       </c>
-      <c r="C273" t="s">
-        <v>503</v>
-      </c>
       <c r="D273" s="1">
         <v>5</v>
       </c>
       <c r="E273" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.45">
@@ -6703,16 +6714,16 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
+        <v>503</v>
+      </c>
+      <c r="C274" t="s">
         <v>504</v>
       </c>
-      <c r="C274" t="s">
-        <v>505</v>
-      </c>
       <c r="D274" s="1">
         <v>1</v>
       </c>
       <c r="E274" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.45">
@@ -6720,16 +6731,16 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
+        <v>505</v>
+      </c>
+      <c r="C275" t="s">
         <v>506</v>
       </c>
-      <c r="C275" t="s">
-        <v>507</v>
-      </c>
       <c r="D275" s="1">
         <v>5</v>
       </c>
       <c r="E275" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.45">
@@ -6737,16 +6748,16 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
+        <v>507</v>
+      </c>
+      <c r="C276" t="s">
         <v>508</v>
       </c>
-      <c r="C276" t="s">
-        <v>509</v>
-      </c>
       <c r="D276" s="1">
         <v>1</v>
       </c>
       <c r="E276" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.45">
@@ -6754,16 +6765,16 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
+        <v>509</v>
+      </c>
+      <c r="C277" t="s">
         <v>510</v>
       </c>
-      <c r="C277" t="s">
-        <v>511</v>
-      </c>
       <c r="D277" s="1">
         <v>1</v>
       </c>
       <c r="E277" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.45">
@@ -6771,16 +6782,16 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
+        <v>511</v>
+      </c>
+      <c r="C278" t="s">
         <v>512</v>
       </c>
-      <c r="C278" t="s">
-        <v>513</v>
-      </c>
       <c r="D278" s="1">
         <v>1</v>
       </c>
       <c r="E278" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.45">
@@ -6788,16 +6799,16 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
+        <v>513</v>
+      </c>
+      <c r="C279" t="s">
         <v>514</v>
-      </c>
-      <c r="C279" t="s">
-        <v>515</v>
       </c>
       <c r="D279" s="1">
         <v>2</v>
       </c>
       <c r="E279" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.45">
@@ -6805,16 +6816,16 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
+        <v>515</v>
+      </c>
+      <c r="C280" t="s">
         <v>516</v>
       </c>
-      <c r="C280" t="s">
-        <v>517</v>
-      </c>
       <c r="D280" s="1">
         <v>4</v>
       </c>
       <c r="E280" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.45">
@@ -6822,16 +6833,16 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
+        <v>517</v>
+      </c>
+      <c r="C281" t="s">
         <v>518</v>
-      </c>
-      <c r="C281" t="s">
-        <v>519</v>
       </c>
       <c r="D281" s="1">
         <v>3</v>
       </c>
       <c r="E281" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.45">
@@ -6839,16 +6850,16 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
+        <v>519</v>
+      </c>
+      <c r="C282" t="s">
         <v>520</v>
       </c>
-      <c r="C282" t="s">
-        <v>521</v>
-      </c>
       <c r="D282" s="1">
         <v>1</v>
       </c>
       <c r="E282" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.45">
@@ -6856,16 +6867,16 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
+        <v>521</v>
+      </c>
+      <c r="C283" t="s">
         <v>522</v>
       </c>
-      <c r="C283" t="s">
-        <v>523</v>
-      </c>
       <c r="D283" s="1">
         <v>5</v>
       </c>
       <c r="E283" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.45">
@@ -6873,16 +6884,16 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
+        <v>523</v>
+      </c>
+      <c r="C284" t="s">
         <v>524</v>
-      </c>
-      <c r="C284" t="s">
-        <v>525</v>
       </c>
       <c r="D284" s="1">
         <v>3</v>
       </c>
       <c r="E284" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.45">
@@ -6890,16 +6901,16 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
+        <v>525</v>
+      </c>
+      <c r="C285" t="s">
         <v>526</v>
-      </c>
-      <c r="C285" t="s">
-        <v>527</v>
       </c>
       <c r="D285" s="1">
         <v>2</v>
       </c>
       <c r="E285" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.45">
@@ -6907,16 +6918,16 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
+        <v>527</v>
+      </c>
+      <c r="C286" t="s">
         <v>528</v>
-      </c>
-      <c r="C286" t="s">
-        <v>529</v>
       </c>
       <c r="D286" s="1">
         <v>3</v>
       </c>
       <c r="E286" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.45">
@@ -6924,16 +6935,16 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
+        <v>529</v>
+      </c>
+      <c r="C287" t="s">
         <v>530</v>
       </c>
-      <c r="C287" t="s">
-        <v>531</v>
-      </c>
       <c r="D287" s="1">
         <v>1</v>
       </c>
       <c r="E287" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
